--- a/minRead_pcb_V2.xlsx
+++ b/minRead_pcb_V2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deangao/UNSYNC/U_PROJECTS/de-link-pcb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78E372EE-C117-A440-93D6-A90D4FE0F571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{95FE05BA-137C-3649-AEC6-0C8807F59A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="160" windowWidth="25380" windowHeight="28480" xr2:uid="{CA0ADED3-AF3E-874A-A6DE-3CDEF6CFE11F}"/>
+    <workbookView xWindow="160" yWindow="820" windowWidth="16860" windowHeight="21160" xr2:uid="{CA0ADED3-AF3E-874A-A6DE-3CDEF6CFE11F}"/>
   </bookViews>
   <sheets>
     <sheet name="minRead_pcb" sheetId="1" r:id="rId1"/>
@@ -352,9 +352,6 @@
     <t>SW6</t>
   </si>
   <si>
-    <t>Button_Switch_THT:SW_PUSH_6mm</t>
-  </si>
-  <si>
     <t>U1,U6</t>
   </si>
   <si>
@@ -407,6 +404,9 @@
   </si>
   <si>
     <t>TP4054</t>
+  </si>
+  <si>
+    <t>Button_Switch_THT:SW_PUSH_1P1T_6x3.5mm_H4.3_APEM_MJTP1243</t>
   </si>
 </sst>
 </file>
@@ -1502,7 +1502,7 @@
       <c r="A15" t="s">
         <v>41</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="1">
         <v>1</v>
       </c>
       <c r="C15" t="s">
@@ -1547,7 +1547,7 @@
       <c r="A18" t="s">
         <v>51</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="2">
         <v>1</v>
       </c>
       <c r="C18" t="s">
@@ -1893,6 +1893,9 @@
       <c r="C41" t="s">
         <v>107</v>
       </c>
+      <c r="D41">
+        <v>10</v>
+      </c>
       <c r="G41" t="s">
         <v>108</v>
       </c>
@@ -1911,89 +1914,89 @@
         <v>3</v>
       </c>
       <c r="G42" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B43" s="1">
         <v>2</v>
       </c>
       <c r="C43" t="s">
+        <v>111</v>
+      </c>
+      <c r="G43" t="s">
         <v>112</v>
-      </c>
-      <c r="G43" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
+        <v>113</v>
+      </c>
+      <c r="B44" s="1">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
         <v>114</v>
       </c>
-      <c r="B44" s="1">
-        <v>1</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="G44" t="s">
         <v>115</v>
       </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
         <v>116</v>
-      </c>
-      <c r="H44" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
+        <v>117</v>
+      </c>
+      <c r="B45" s="2">
+        <v>1</v>
+      </c>
+      <c r="C45" t="s">
         <v>118</v>
       </c>
-      <c r="B45">
-        <v>1</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="G45" t="s">
         <v>119</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
         <v>120</v>
-      </c>
-      <c r="H45" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
+        <v>121</v>
+      </c>
+      <c r="B46" s="2">
+        <v>1</v>
+      </c>
+      <c r="C46" t="s">
+        <v>127</v>
+      </c>
+      <c r="G46" t="s">
         <v>122</v>
       </c>
-      <c r="B46" s="2">
-        <v>1</v>
-      </c>
-      <c r="C46" t="s">
-        <v>128</v>
-      </c>
-      <c r="G46" t="s">
+      <c r="H46" t="s">
         <v>123</v>
-      </c>
-      <c r="H46" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
+        <v>124</v>
+      </c>
+      <c r="B47" s="2">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
         <v>125</v>
       </c>
-      <c r="B47">
-        <v>1</v>
-      </c>
-      <c r="C47" t="s">
+      <c r="G47" t="s">
+        <v>112</v>
+      </c>
+      <c r="H47" t="s">
         <v>126</v>
-      </c>
-      <c r="G47" t="s">
-        <v>113</v>
-      </c>
-      <c r="H47" t="s">
-        <v>127</v>
       </c>
     </row>
   </sheetData>
